--- a/data/trans_camb/P36BPD07_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P36BPD07_R-Edad-trans_camb.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0,23</t>
+          <t>-2,05</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>-9,36</t>
+          <t>-11,53</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-4,33</t>
+          <t>-6,63</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,05; 10,47</t>
+          <t>-10,25; 7,37</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-18,41; -1,29</t>
+          <t>-20,19; -4,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,77; 1,71</t>
+          <t>-12,67; -0,43</t>
         </is>
       </c>
     </row>
@@ -594,17 +594,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>-3,08%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-12,66%</t>
+          <t>-15,6%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-6,16%</t>
+          <t>-9,44%</t>
         </is>
       </c>
     </row>
@@ -617,17 +617,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-13,13; 16,65</t>
+          <t>-14,76; 11,24</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-24,24; -1,82</t>
+          <t>-26,45; -5,72</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-14,87; 2,6</t>
+          <t>-17,67; -0,59</t>
         </is>
       </c>
     </row>
@@ -644,17 +644,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>-12,95</t>
+          <t>-11,62</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,56</t>
+          <t>-3,37</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-5,46</t>
+          <t>-7,36</t>
         </is>
       </c>
     </row>
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-20,99; -6,1</t>
+          <t>-18,94; -5,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,44; 9,91</t>
+          <t>-8,18; 2,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,08; 1,73</t>
+          <t>-11,51; -3,26</t>
         </is>
       </c>
     </row>
@@ -690,17 +690,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>-17,07%</t>
+          <t>-15,32%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>-4,35%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-7,12%</t>
+          <t>-9,59%</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-27,34; -8,34</t>
+          <t>-23,98; -7,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,85; 13,03</t>
+          <t>-10,28; 3,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-12,88; 2,37</t>
+          <t>-14,74; -4,21</t>
         </is>
       </c>
     </row>
@@ -740,17 +740,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>-12,24</t>
+          <t>-13,42</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>-9,14</t>
+          <t>-9,27</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-10,69</t>
+          <t>-11,35</t>
         </is>
       </c>
     </row>
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-17,44; -7,61</t>
+          <t>-18,43; -8,46</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-13,39; -4,58</t>
+          <t>-13,84; -4,85</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-14,12; -7,51</t>
+          <t>-14,76; -8,11</t>
         </is>
       </c>
     </row>
@@ -786,17 +786,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>-14,75%</t>
+          <t>-16,18%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>-11,21%</t>
+          <t>-11,36%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-12,99%</t>
+          <t>-13,79%</t>
         </is>
       </c>
     </row>
@@ -809,17 +809,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-20,55; -9,37</t>
+          <t>-21,82; -10,45</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-16,05; -5,69</t>
+          <t>-16,61; -6,2</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-16,92; -9,24</t>
+          <t>-17,6; -10,02</t>
         </is>
       </c>
     </row>
@@ -836,17 +836,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>-6,28</t>
+          <t>-14,59</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>-11,35</t>
+          <t>-13,5</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-8,74</t>
+          <t>-13,99</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-15,76; 6,37</t>
+          <t>-19,21; -10,12</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-14,98; -6,51</t>
+          <t>-16,65; -9,68</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-13,9; -0,83</t>
+          <t>-16,52; -10,81</t>
         </is>
       </c>
     </row>
@@ -882,17 +882,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>-7,34%</t>
+          <t>-17,06%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>-12,72%</t>
+          <t>-15,13%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-10,0%</t>
+          <t>-16,01%</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-18,28; 7,59</t>
+          <t>-22,09; -12,17</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-16,48; -7,35</t>
+          <t>-18,54; -11,16</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-15,79; -0,95</t>
+          <t>-18,62; -12,57</t>
         </is>
       </c>
     </row>
@@ -932,17 +932,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>-20,96</t>
+          <t>-21,15</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>-14,45</t>
+          <t>-14,46</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-17,71</t>
+          <t>-17,79</t>
         </is>
       </c>
     </row>
@@ -955,17 +955,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-24,9; -16,92</t>
+          <t>-24,98; -17,1</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-17,61; -10,61</t>
+          <t>-17,52; -11,3</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-20,19; -14,92</t>
+          <t>-20,49; -15,37</t>
         </is>
       </c>
     </row>
@@ -978,17 +978,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>-21,85%</t>
+          <t>-22,05%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>-15,3%</t>
+          <t>-15,32%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-18,61%</t>
+          <t>-18,69%</t>
         </is>
       </c>
     </row>
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-25,72; -17,89</t>
+          <t>-25,92; -18,13</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-18,38; -11,42</t>
+          <t>-18,34; -12,21</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-21,09; -16,01</t>
+          <t>-21,38; -16,33</t>
         </is>
       </c>
     </row>
@@ -1028,17 +1028,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>-17,04</t>
+          <t>-16,9</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>-8,85</t>
+          <t>-14,78</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-11,85</t>
+          <t>-15,81</t>
         </is>
       </c>
     </row>
@@ -1051,17 +1051,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-21,1; -13,11</t>
+          <t>-20,98; -13,12</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-15,36; -0,18</t>
+          <t>-17,8; -11,61</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-16,46; -4,14</t>
+          <t>-18,31; -13,47</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>-17,59%</t>
+          <t>-17,45%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>-9,05%</t>
+          <t>-15,12%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-12,17%</t>
+          <t>-16,25%</t>
         </is>
       </c>
     </row>
@@ -1097,17 +1097,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-21,57; -13,63</t>
+          <t>-21,58; -13,81</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-15,66; -0,2</t>
+          <t>-18,17; -12,07</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-16,88; -4,29</t>
+          <t>-18,65; -13,92</t>
         </is>
       </c>
     </row>
@@ -1124,17 +1124,17 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>-17,39</t>
+          <t>-17,68</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>-12,14</t>
+          <t>-12,54</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-14,24</t>
+          <t>-14,6</t>
         </is>
       </c>
     </row>
@@ -1147,17 +1147,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-21,88; -13,25</t>
+          <t>-22,57; -13,45</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-15,31; -9,07</t>
+          <t>-15,41; -9,71</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-16,68; -11,54</t>
+          <t>-16,97; -12,13</t>
         </is>
       </c>
     </row>
@@ -1170,17 +1170,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>-17,98%</t>
+          <t>-18,27%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>-12,51%</t>
+          <t>-12,92%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-14,69%</t>
+          <t>-15,06%</t>
         </is>
       </c>
     </row>
@@ -1193,17 +1193,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-22,46; -13,94</t>
+          <t>-23,13; -14,05</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-15,67; -9,46</t>
+          <t>-15,67; -10,05</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-17,09; -12,08</t>
+          <t>-17,38; -12,58</t>
         </is>
       </c>
     </row>
@@ -1220,17 +1220,17 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>-10,52</t>
+          <t>-12,92</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>-7,79</t>
+          <t>-10,43</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-9,11</t>
+          <t>-11,64</t>
         </is>
       </c>
     </row>
@@ -1243,17 +1243,17 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-13,29; -4,2</t>
+          <t>-14,96; -10,82</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-10,15; -4,09</t>
+          <t>-12,25; -8,73</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-11,06; -5,98</t>
+          <t>-12,87; -10,23</t>
         </is>
       </c>
     </row>
@@ -1266,17 +1266,17 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>-12,46%</t>
+          <t>-15,31%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>-8,98%</t>
+          <t>-12,03%</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-10,64%</t>
+          <t>-13,6%</t>
         </is>
       </c>
     </row>
@@ -1289,17 +1289,17 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-15,66; -4,98</t>
+          <t>-17,6; -12,91</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-11,64; -4,74</t>
+          <t>-14,01; -10,17</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-12,85; -7,0</t>
+          <t>-15,01; -12,05</t>
         </is>
       </c>
     </row>
